--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -630,12 +630,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BearingPoint</t>
+          <t>Agile Robots</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>(Senior) Consultant / Architect ServiceNow Banking &amp; Insurance (m/w/d) Berlin, Düsseldorf, Frankfurt am Main, Hamburg, Leipzig, München, Stuttgart, Walldorf</t>
+          <t>Senior Project Manager (all genders)</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -653,29 +653,29 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Berlin, DE; Düsseldorf, DE; Frankfurt am Main, DE; Hamburg, DE; Leipzig, DE; München, DE; Stuttgart, DE; Walldorf, DE</t>
+          <t>Munich, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.bearingpoint.com/de-de/karriere/stellenangebote/angebot/?id=T7549597</t>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4990647101</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Related role</t>
+          <t>Direct role</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Responsibilities: delivery, transformation</t>
+          <t>Title: project manager</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -690,11 +690,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Senior Project Manager (all genders)</t>
+          <t>(Senior) Technical Program Manager (m/f/d)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4990647101</t>
+          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4996481101</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -713,19 +713,19 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Title: project manager</t>
+          <t>Title: program manager</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Celonis</t>
+          <t>Proxima Fusion</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -735,480 +735,120 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Senior Business Transformation &amp; Process Optimisation Consultant - Aviation/Logistics</t>
+          <t>Site Development Program Manager</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Munich, Germany</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/8015653003?gh_jid=8015653003</t>
+          <t>https://jobs.ashbyhq.com/proxima-fusion/db5bc40c-aa3e-4735-94e7-096a556dd55d</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Related role</t>
+          <t>Direct role</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Responsibilities: delivery, stakeholders, transformation</t>
+          <t>Title: program manager</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Senior Digital Transformation &amp; Process Optimisation Consultant - CPG/Retail</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/8016417003?gh_jid=8016417003</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Related role</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Responsibilities: delivery, stakeholders, transformation</t>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>LCA &amp; Environmental Data Specialist (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Parsdorf, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/5009959101</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Title: environmental</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Senior Management &amp; Technology Consultant - Aviation/Logistics</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Environmental Management Specialist (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/8015654003?gh_jid=8015654003</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Related role</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Responsibilities: delivery, stakeholders, transformation</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Senior Management &amp; Technology Consultant - CPG/Retail - CPG/Retail</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/8016657003?gh_jid=8016657003</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Related role</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Responsibilities: delivery, stakeholders, transformation</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Senior Management &amp; Technology Consultant - Growth &amp; Scale Accounts</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>4</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/8026730003?gh_jid=8026730003</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Related role</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Responsibilities: governance, stakeholders, transformation</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Senior Process Intelligence &amp; Supply Chain Transformation Consultant - Aviation/Logistics</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>4</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/8015655003?gh_jid=8015655003</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Related role</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Responsibilities: delivery, stakeholders, transformation</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Senior Process Intelligence &amp; Supply Chain Transformation Consultant - CPG/Retail</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>4</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/8016658003?gh_jid=8016658003</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Related role</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Responsibilities: delivery, stakeholders, transformation</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Senior Process Optimisation Consultant - Growth &amp; Scale Accounts</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>4</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/8026747003?gh_jid=8026747003</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Related role</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Responsibilities: governance, stakeholders, transformation</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Agile Robots</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>(Senior) Technical Program Manager (m/f/d)</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Munich, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4996481101</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Parsdorf, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/5009977101</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Direct role</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Title: program manager</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Proxima Fusion</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Site Development Program Manager</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>3</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/proxima-fusion/db5bc40c-aa3e-4735-94e7-096a556dd55d</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Title: program manager</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Isar Aerospace</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>MES Delivery Manager / Project Manager (m/f/d)</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>8</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Parsdorf, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4989582101</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Title: project manager</t>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Title: environmental</t>
         </is>
       </c>
     </row>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -495,12 +495,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Helsing</t>
+          <t>ARX Robotics</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -510,11 +510,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>(Senior) Programme Manager - Military Exercises</t>
+          <t>Project Manager - Infrastructure &amp; Expansion</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -523,7 +523,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://helsing.ai/jobs/5004102101?gh_jid=5004102101</t>
+          <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/5005798101</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -533,19 +533,19 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Title: programme manager</t>
+          <t>Title: project manager</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ARX Robotics</t>
+          <t>Proxima Fusion</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -555,11 +555,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Project Manager - Infrastructure &amp; Expansion</t>
+          <t>Site Development Program Manager</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -568,7 +568,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/5005798101</t>
+          <t>https://jobs.ashbyhq.com/proxima-fusion/db5bc40c-aa3e-4735-94e7-096a556dd55d</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -578,19 +578,19 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Title: project manager</t>
+          <t>Title: program manager</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Helsing</t>
+          <t>Isar Aerospace</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -600,20 +600,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Senior Programme Manager - International Business Development Air</t>
+          <t>LCA &amp; Environmental Data Specialist (f/m/d)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://helsing.ai/jobs/5001597101?gh_jid=5001597101</t>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/5009959101</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -623,19 +623,19 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Title: programme manager</t>
+          <t>Title: environmental</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Agile Robots</t>
+          <t>Isar Aerospace</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -645,20 +645,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Senior Project Manager (all genders)</t>
+          <t>Environmental Management Specialist (f/m/d)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Munich, Bavaria, Germany</t>
+          <t>Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4990647101</t>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/5009977101</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -667,186 +667,6 @@
         </is>
       </c>
       <c r="I5" t="inlineStr">
-        <is>
-          <t>Title: project manager</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Agile Robots</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>(Senior) Technical Program Manager (m/f/d)</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Munich, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/agilerobotsse/jobs/4996481101</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Title: program manager</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Proxima Fusion</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Site Development Program Manager</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/proxima-fusion/db5bc40c-aa3e-4735-94e7-096a556dd55d</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Title: program manager</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Isar Aerospace</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>LCA &amp; Environmental Data Specialist (f/m/d)</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Parsdorf, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/5009959101</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>Title: environmental</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Isar Aerospace</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Environmental Management Specialist (f/m/d)</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Parsdorf, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/5009977101</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>Title: environmental</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -41,12 +41,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D1FAE5"/>
-        <bgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
   </fills>
@@ -62,10 +56,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -492,186 +485,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>ARX Robotics</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Project Manager - Infrastructure &amp; Expansion</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/5005798101</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Title: project manager</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Proxima Fusion</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Site Development Program Manager</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/proxima-fusion/db5bc40c-aa3e-4735-94e7-096a556dd55d</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Title: program manager</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Isar Aerospace</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LCA &amp; Environmental Data Specialist (f/m/d)</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>10</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Parsdorf, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/5009959101</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Title: environmental</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Isar Aerospace</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Environmental Management Specialist (f/m/d)</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Parsdorf, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/5009977101</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Title: environmental</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +41,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
   </fills>
@@ -56,9 +62,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -485,6 +492,96 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>LCA &amp; Environmental Data Specialist (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Parsdorf, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/5009959101</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Title: environmental</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Environmental Management Specialist (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Parsdorf, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/5009977101</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Title: environmental</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -493,90 +493,90 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>LCA &amp; Environmental Data Specialist (f/m/d)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" t="n">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/5009959101</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Direct role</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Title: environmental</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Environmental Management Specialist (f/m/d)</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" t="n">
         <v>4</v>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/5009977101</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Direct role</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Title: environmental</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -510,11 +510,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LCA &amp; Environmental Data Specialist (f/m/d)</t>
+          <t>Environmental Management Specialist (f/m/d)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -523,7 +523,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/5009959101</t>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/5009977101</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -532,51 +532,6 @@
         </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>Title: environmental</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Isar Aerospace</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Environmental Management Specialist (f/m/d)</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>4</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Parsdorf, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/5009977101</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
         <is>
           <t>Title: environmental</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -493,47 +493,530 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Data Analyst</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Lisbon (Airbus Portugal); Coimbra</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Lisbon-Airbus-Portugal/Procurement-Data-Analyst_JR10446958</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Lisbon (Airbus Portugal); Coimbra</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>STAGE 2027 - Scénarios prospectifs pour l'aviation : analyse énergétique et décarbonation (F/H)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Toulouse Area</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Toulouse-Area/STAGE-2027---Scnarios-prospectifs-pour-l-aviation---analyse-nergtique-et-dcarbonation--F-H-_JR10443850</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Title: carbon | LOCATION UNVERIFIED: Toulouse Area</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Environmental Test Engineer</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Stevenage</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Stevenage/Environmental-Test-Engineer_JR10408723</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Title: environmental | LOCATION UNVERIFIED: Stevenage</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Amgen Munich</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Environmental Health &amp; Safety Manager</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>US - California - South San Francisco</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>https://amgen.wd1.myworkdayjobs.com/Careers/job/US---California---South-San-Francisco/Environmental-Health---Safety-Manager_R-258423-1</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Title: environmental | LOCATION UNVERIFIED: US - California - South San Francisco</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>Environmental Management Specialist (f/m/d)</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E6" t="n">
         <v>4</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/5009977101</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>Title: environmental</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>FlixMobility</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Data Analyst Mexico City Regular</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Mexico City</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>https://flix.careers/job/?jobid=8364246002</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Mexico City</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>FlixMobility</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Jr. Financial Planning &amp; Reporting Specialist (m/f/d) Sofia Regular</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>https://flix.careers/job/?jobid=8891299002</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Title: reporting specialist | LOCATION UNVERIFIED: Sofia</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>FlixMobility</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Jr. Financial Planning &amp; Reporting Specialist (m/f/d) Sofia Regular</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>https://flix.careers/job/?jobid=8622257002</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Title: reporting specialist | LOCATION UNVERIFIED: Sofia</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Stryker Munich</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Service Associate - Detroit, MI - Sustainability Solutions</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Detroit, Michigan</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>https://stryker.wd1.myworkdayjobs.com/StrykerCareers/job/Detroit-Michigan/Service-Associate---Detroit--MI---Sustainability-Solutions_R576161</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Title: sustainability | LOCATION UNVERIFIED: Detroit, Michigan</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Stryker Munich</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Service Associate - Salt Lake City, Utah - Sustainability Solutions</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Salt Lake City, Utah</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>https://stryker.wd1.myworkdayjobs.com/StrykerCareers/job/Salt-Lake-City-Utah/Service-Associate---Salt-Lake-City--Utah---Sustainability-Solutions_R575799</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Title: sustainability | LOCATION UNVERIFIED: Salt Lake City, Utah</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Stage 2027 - Stagiaire en Atténuation des effets non-CO2 de l'aviation (F/H)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Toulouse Area</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Toulouse-Area/Stage-2027---Stagiaire-en-Attnuation-des-effets-non-CO2-de-l-aviation--F-H-_JR10443593</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Title: co2 | LOCATION UNVERIFIED: Toulouse Area</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Combat Business Planning and Reporting Analyst (Temp Agency)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Getafe Area</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Getafe-Area/Combat-Business-Planning-and-Reporting-Analyst--Temp-Agency-_JR10450246</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Title: reporting analyst | LOCATION UNVERIFIED: Getafe Area</t>
         </is>
       </c>
     </row>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -493,182 +493,178 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr"/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>gridX</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Initiativbewerbung (all genders) - Gestalte mit uns die Energiewende</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Remote DE; Aachen; Munich</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>https://gridx.jobs.personio.de/job/2723197</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Title: energiewende</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Airbus</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>Procurement Data Analyst</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E3" t="n">
         <v>8</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Lisbon (Airbus Portugal); Coimbra</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Lisbon-Airbus-Portugal/Procurement-Data-Analyst_JR10446958</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>Title: data analyst | LOCATION UNVERIFIED: Lisbon (Airbus Portugal); Coimbra</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Airbus</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>STAGE 2027 - Scénarios prospectifs pour l'aviation : analyse énergétique et décarbonation (F/H)</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E4" t="n">
         <v>8</v>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Toulouse Area</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Toulouse-Area/STAGE-2027---Scnarios-prospectifs-pour-l-aviation---analyse-nergtique-et-dcarbonation--F-H-_JR10443850</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>Title: carbon | LOCATION UNVERIFIED: Toulouse Area</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Airbus</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>Environmental Test Engineer</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E5" t="n">
         <v>5</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Stevenage</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Stevenage/Environmental-Test-Engineer_JR10408723</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>Title: environmental | LOCATION UNVERIFIED: Stevenage</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Amgen Munich</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Environmental Health &amp; Safety Manager</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>US - California - South San Francisco</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>https://amgen.wd1.myworkdayjobs.com/Careers/job/US---California---South-San-Francisco/Environmental-Health---Safety-Manager_R-258423-1</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Title: environmental | LOCATION UNVERIFIED: US - California - South San Francisco</t>
         </is>
       </c>
     </row>
@@ -680,343 +676,561 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>Amgen Munich</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Environmental Health &amp; Safety Manager</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>US - California - South San Francisco</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://amgen.wd1.myworkdayjobs.com/Careers/job/US---California---South-San-Francisco/Environmental-Health---Safety-Manager_R-258423-1</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Title: environmental | LOCATION UNVERIFIED: US - California - South San Francisco</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>Environmental Management Specialist (f/m/d)</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E7" t="n">
         <v>4</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/5009977101</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>Title: environmental</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
-      <c r="B7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>FlixMobility</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>Commercial Data Analyst Mexico City Regular</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E8" t="n">
         <v>4</v>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Mexico City</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://flix.careers/job/?jobid=8364246002</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>Title: data analyst | LOCATION UNVERIFIED: Mexico City</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
-      <c r="B8" s="2" t="inlineStr">
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>FlixMobility</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>Jr. Financial Planning &amp; Reporting Specialist (m/f/d) Sofia Regular</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E9" t="n">
         <v>4</v>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Sofia</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://flix.careers/job/?jobid=8891299002</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>Title: reporting specialist | LOCATION UNVERIFIED: Sofia</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr"/>
-      <c r="B9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="B10" t="inlineStr">
         <is>
           <t>FlixMobility</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>Jr. Financial Planning &amp; Reporting Specialist (m/f/d) Sofia Regular</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E10" t="n">
         <v>4</v>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Sofia</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://flix.careers/job/?jobid=8622257002</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>Title: reporting specialist | LOCATION UNVERIFIED: Sofia</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Stryker Munich</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>Service Associate - Detroit, MI - Sustainability Solutions</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E11" t="n">
         <v>4</v>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Detroit, Michigan</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>https://stryker.wd1.myworkdayjobs.com/StrykerCareers/job/Detroit-Michigan/Service-Associate---Detroit--MI---Sustainability-Solutions_R576161</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>Title: sustainability | LOCATION UNVERIFIED: Detroit, Michigan</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Stryker Munich</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>Service Associate - Salt Lake City, Utah - Sustainability Solutions</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E12" t="n">
         <v>4</v>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Salt Lake City, Utah</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>https://stryker.wd1.myworkdayjobs.com/StrykerCareers/job/Salt-Lake-City-Utah/Service-Associate---Salt-Lake-City--Utah---Sustainability-Solutions_R575799</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>Title: sustainability | LOCATION UNVERIFIED: Salt Lake City, Utah</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Airbus</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>Stage 2027 - Stagiaire en Atténuation des effets non-CO2 de l'aviation (F/H)</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E13" t="n">
         <v>3</v>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Toulouse Area</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Toulouse-Area/Stage-2027---Stagiaire-en-Attnuation-des-effets-non-CO2-de-l-aviation--F-H-_JR10443593</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>Title: co2 | LOCATION UNVERIFIED: Toulouse Area</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Airbus</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>Combat Business Planning and Reporting Analyst (Temp Agency)</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E14" t="n">
         <v>3</v>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Getafe Area</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Getafe-Area/Combat-Business-Planning-and-Reporting-Analyst--Temp-Agency-_JR10450246</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
         <is>
           <t>Title: reporting analyst | LOCATION UNVERIFIED: Getafe Area</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>STAGE 2027 - Data Analyste en qualité logistique (h/f)</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Tremblay-en-France</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Tremblay-en-France/STAGE-2027---Data-Analyste-en-qualit-logistique--h-f-_JR10443345</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Tremblay-en-France</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>STAGE 2027 - Finance Data Analyst (m/f)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Marseille Area</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Marseille-Area/XMLNAME---Internship---Offer-Evaluation-digitalization---Finance-BI-Analyst--m-f--_JR10443902</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Marseille Area</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Sun Oct 25 02:00:00 UTC 2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Systemingenieur für Radar Environmental Simulator (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/Ulm-Systemingenieur-f%C3%BCr-Radar-Environmental-Simulator-%28wmd%29-89077/1365917055/</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Title: environmental | LOCATION UNVERIFIED: none</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Workday Munich</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Reporting Analyst, Workday Reporting</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>IND.Pune</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>https://workday.wd5.myworkdayjobs.com/Workday/job/INDPune/Reporting-Analyst--Workday-Reporting_JR-0110733</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Title: reporting analyst | LOCATION UNVERIFIED: IND.Pune</t>
         </is>
       </c>
     </row>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -493,41 +493,40 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>gridX</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>Initiativbewerbung (all genders) - Gestalte mit uns die Energiewende</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" t="n">
         <v>4</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Remote DE; Aachen; Munich</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>https://gridx.jobs.personio.de/job/2723197</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>Title: energiewende</t>
         </is>
@@ -624,59 +623,59 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Airbus</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Environmental Test Engineer</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Stevenage</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Stevenage/Environmental-Test-Engineer_JR10408723</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Title: environmental | LOCATION UNVERIFIED: Stevenage</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Siemens Energy</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Data Analyst im Bereich Manufacturing (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Data-Analyst-im-Bereich-Manufacturing-m-w-d/305767</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Germany</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Amgen Munich</t>
+          <t>Airbus</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -686,7 +685,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Environmental Health &amp; Safety Manager</t>
+          <t>Environmental Test Engineer</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -694,12 +693,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>US - California - South San Francisco</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://amgen.wd1.myworkdayjobs.com/Careers/job/US---California---South-San-Francisco/Environmental-Health---Safety-Manager_R-258423-1</t>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Stevenage/Environmental-Test-Engineer_JR10408723</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -709,7 +708,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Title: environmental | LOCATION UNVERIFIED: US - California - South San Francisco</t>
+          <t>Title: environmental | LOCATION UNVERIFIED: Stevenage</t>
         </is>
       </c>
     </row>
@@ -721,57 +720,62 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>Amgen Munich</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Environmental Health &amp; Safety Manager</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>US - California - South San Francisco</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://amgen.wd1.myworkdayjobs.com/Careers/job/US---California---South-San-Francisco/Environmental-Health---Safety-Manager_R-258423-1</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Title: environmental | LOCATION UNVERIFIED: US - California - South San Francisco</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>Environmental Management Specialist (f/m/d)</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Parsdorf, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/5009977101</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Title: environmental</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>FlixMobility</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Commercial Data Analyst Mexico City Regular</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -779,12 +783,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mexico City</t>
+          <t>Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://flix.careers/job/?jobid=8364246002</t>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/5009977101</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -794,7 +798,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Title: data analyst | LOCATION UNVERIFIED: Mexico City</t>
+          <t>Title: environmental</t>
         </is>
       </c>
     </row>
@@ -811,7 +815,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Jr. Financial Planning &amp; Reporting Specialist (m/f/d) Sofia Regular</t>
+          <t>Commercial Data Analyst Mexico City Regular</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -819,12 +823,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sofia</t>
+          <t>Mexico City</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://flix.careers/job/?jobid=8891299002</t>
+          <t>https://flix.careers/job/?jobid=8364246002</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -834,7 +838,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Title: reporting specialist | LOCATION UNVERIFIED: Sofia</t>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Mexico City</t>
         </is>
       </c>
     </row>
@@ -864,7 +868,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://flix.careers/job/?jobid=8622257002</t>
+          <t>https://flix.careers/job/?jobid=8891299002</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -879,14 +883,9 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stryker Munich</t>
+          <t>FlixMobility</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -896,7 +895,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Service Associate - Detroit, MI - Sustainability Solutions</t>
+          <t>Jr. Financial Planning &amp; Reporting Specialist (m/f/d) Sofia Regular</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -904,12 +903,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Detroit, Michigan</t>
+          <t>Sofia</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://stryker.wd1.myworkdayjobs.com/StrykerCareers/job/Detroit-Michigan/Service-Associate---Detroit--MI---Sustainability-Solutions_R576161</t>
+          <t>https://flix.careers/job/?jobid=8622257002</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -919,14 +918,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Title: sustainability | LOCATION UNVERIFIED: Detroit, Michigan</t>
+          <t>Title: reporting specialist | LOCATION UNVERIFIED: Sofia</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -941,7 +940,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Service Associate - Salt Lake City, Utah - Sustainability Solutions</t>
+          <t>Service Associate - Detroit, MI - Sustainability Solutions</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -949,12 +948,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Salt Lake City, Utah</t>
+          <t>Detroit, Michigan</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://stryker.wd1.myworkdayjobs.com/StrykerCareers/job/Salt-Lake-City-Utah/Service-Associate---Salt-Lake-City--Utah---Sustainability-Solutions_R575799</t>
+          <t>https://stryker.wd1.myworkdayjobs.com/StrykerCareers/job/Detroit-Michigan/Service-Associate---Detroit--MI---Sustainability-Solutions_R576161</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -964,271 +963,360 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Title: sustainability | LOCATION UNVERIFIED: Salt Lake City, Utah</t>
+          <t>Title: sustainability | LOCATION UNVERIFIED: Detroit, Michigan</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Stryker Munich</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Service Associate - Salt Lake City, Utah - Sustainability Solutions</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Salt Lake City, Utah</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://stryker.wd1.myworkdayjobs.com/StrykerCareers/job/Salt-Lake-City-Utah/Service-Associate---Salt-Lake-City--Utah---Sustainability-Solutions_R575799</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Title: sustainability | LOCATION UNVERIFIED: Salt Lake City, Utah</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>A400M Fleet maintenance data analyst</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Getafe Area</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Getafe-Area/A400M-Fleet-maintenance-data-analyst_JR10448810-1</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Getafe Area</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Airbus</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>Stage 2027 - Stagiaire en Atténuation des effets non-CO2 de l'aviation (F/H)</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E15" t="n">
         <v>3</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Toulouse Area</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Toulouse-Area/Stage-2027---Stagiaire-en-Attnuation-des-effets-non-CO2-de-l-aviation--F-H-_JR10443593</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>Title: co2 | LOCATION UNVERIFIED: Toulouse Area</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Airbus</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>Combat Business Planning and Reporting Analyst (Temp Agency)</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="E16" t="n">
         <v>3</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Getafe Area</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Getafe-Area/Combat-Business-Planning-and-Reporting-Analyst--Temp-Agency-_JR10450246</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t>Title: reporting analyst | LOCATION UNVERIFIED: Getafe Area</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Airbus</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>STAGE 2027 - Data Analyste en qualité logistique (h/f)</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E17" t="n">
         <v>2</v>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Tremblay-en-France</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Tremblay-en-France/STAGE-2027---Data-Analyste-en-qualit-logistique--h-f-_JR10443345</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>Title: data analyst | LOCATION UNVERIFIED: Tremblay-en-France</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Airbus</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>STAGE 2027 - Finance Data Analyst (m/f)</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E18" t="n">
         <v>2</v>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Marseille Area</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Marseille-Area/XMLNAME---Internship---Offer-Evaluation-digitalization---Finance-BI-Analyst--m-f--_JR10443902</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>Title: data analyst | LOCATION UNVERIFIED: Marseille Area</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Sun Oct 25 02:00:00 UTC 2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>Systemingenieur für Radar Environmental Simulator (w/m/d)</t>
         </is>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="E19" t="n">
         <v>2</v>
       </c>
-      <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/Ulm-Systemingenieur-f%C3%BCr-Radar-Environmental-Simulator-%28wmd%29-89077/1365917055/</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>Title: environmental | LOCATION UNVERIFIED: none</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Workday Munich</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>Reporting Analyst, Workday Reporting</t>
         </is>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="E20" t="n">
         <v>2</v>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>IND.Pune</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>https://workday.wd5.myworkdayjobs.com/Workday/job/INDPune/Reporting-Analyst--Workday-Reporting_JR-0110733</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
         <is>
           <t>Title: reporting analyst | LOCATION UNVERIFIED: IND.Pune</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -533,54 +533,54 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Airbus</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Procurement Data Analyst</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Lisbon (Airbus Portugal); Coimbra</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Lisbon-Airbus-Portugal/Procurement-Data-Analyst_JR10446958</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Title: data analyst | LOCATION UNVERIFIED: Lisbon (Airbus Portugal); Coimbra</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Tue Oct 27 02:00:00 UTC 2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>EY Germany</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Manager - Climate Change and Sustainability Services</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Sydney, NSW, AU, 2000 +5 more…</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.ey.com/ey/job/Sydney-Manager-Climate-Change-and-Sustainability-Services-NSW-2000/1441652233/</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Title: sustainability | LOCATION UNVERIFIED: Sydney, NSW, AU, 2000 +5 more…</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>STAGE 2027 - Scénarios prospectifs pour l'aviation : analyse énergétique et décarbonation (F/H)</t>
+          <t>Procurement Data Analyst</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -603,79 +603,79 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>Lisbon (Airbus Portugal); Coimbra</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Lisbon-Airbus-Portugal/Procurement-Data-Analyst_JR10446958</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Lisbon (Airbus Portugal); Coimbra</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>STAGE 2027 - Scénarios prospectifs pour l'aviation : analyse énergétique et décarbonation (F/H)</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>Toulouse Area</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Toulouse-Area/STAGE-2027---Scnarios-prospectifs-pour-l-aviation---analyse-nergtique-et-dcarbonation--F-H-_JR10443850</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>Title: carbon | LOCATION UNVERIFIED: Toulouse Area</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Siemens Energy</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Data Analyst im Bereich Manufacturing (m/w/d)</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Data-Analyst-im-Bereich-Manufacturing-m-w-d/305767</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Title: data analyst | LOCATION UNVERIFIED: Germany</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Airbus</t>
+          <t>Siemens Energy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -685,20 +685,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Environmental Test Engineer</t>
+          <t>Data Analyst im Bereich Manufacturing (m/w/d)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Stevenage/Environmental-Test-Engineer_JR10408723</t>
+          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Data-Analyst-im-Bereich-Manufacturing-m-w-d/305767</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -708,19 +708,19 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Title: environmental | LOCATION UNVERIFIED: Stevenage</t>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Germany</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Amgen Munich</t>
+          <t>Airbus</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Environmental Health &amp; Safety Manager</t>
+          <t>Environmental Test Engineer</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -738,12 +738,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>US - California - South San Francisco</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://amgen.wd1.myworkdayjobs.com/Careers/job/US---California---South-San-Francisco/Environmental-Health---Safety-Manager_R-258423-1</t>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Stevenage/Environmental-Test-Engineer_JR10408723</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -753,69 +753,74 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Title: environmental | LOCATION UNVERIFIED: US - California - South San Francisco</t>
+          <t>Title: environmental | LOCATION UNVERIFIED: Stevenage</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Amgen Munich</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Environmental Health &amp; Safety Manager</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>US - California - South San Francisco</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://amgen.wd1.myworkdayjobs.com/Careers/job/US---California---South-San-Francisco/Environmental-Health---Safety-Manager_R-258423-1</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Title: environmental | LOCATION UNVERIFIED: US - California - South San Francisco</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>Environmental Management Specialist (f/m/d)</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Parsdorf, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/5009977101</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Title: environmental</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>FlixMobility</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Commercial Data Analyst Mexico City Regular</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -823,12 +828,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mexico City</t>
+          <t>Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://flix.careers/job/?jobid=8364246002</t>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/5009977101</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -838,7 +843,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Title: data analyst | LOCATION UNVERIFIED: Mexico City</t>
+          <t>Title: environmental</t>
         </is>
       </c>
     </row>
@@ -855,7 +860,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Jr. Financial Planning &amp; Reporting Specialist (m/f/d) Sofia Regular</t>
+          <t>Commercial Data Analyst Mexico City Regular</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -863,12 +868,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sofia</t>
+          <t>Mexico City</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://flix.careers/job/?jobid=8891299002</t>
+          <t>https://flix.careers/job/?jobid=8364246002</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -878,7 +883,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Title: reporting specialist | LOCATION UNVERIFIED: Sofia</t>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Mexico City</t>
         </is>
       </c>
     </row>
@@ -908,7 +913,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://flix.careers/job/?jobid=8622257002</t>
+          <t>https://flix.careers/job/?jobid=8891299002</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -923,14 +928,9 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Stryker Munich</t>
+          <t>FlixMobility</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Service Associate - Detroit, MI - Sustainability Solutions</t>
+          <t>Jr. Financial Planning &amp; Reporting Specialist (m/f/d) Sofia Regular</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -948,12 +948,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Detroit, Michigan</t>
+          <t>Sofia</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://stryker.wd1.myworkdayjobs.com/StrykerCareers/job/Detroit-Michigan/Service-Associate---Detroit--MI---Sustainability-Solutions_R576161</t>
+          <t>https://flix.careers/job/?jobid=8622257002</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -963,14 +963,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Title: sustainability | LOCATION UNVERIFIED: Detroit, Michigan</t>
+          <t>Title: reporting specialist | LOCATION UNVERIFIED: Sofia</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Service Associate - Salt Lake City, Utah - Sustainability Solutions</t>
+          <t>Service Associate - Detroit, MI - Sustainability Solutions</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -993,74 +993,74 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>Detroit, Michigan</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://stryker.wd1.myworkdayjobs.com/StrykerCareers/job/Detroit-Michigan/Service-Associate---Detroit--MI---Sustainability-Solutions_R576161</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Title: sustainability | LOCATION UNVERIFIED: Detroit, Michigan</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Stryker Munich</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Service Associate - Salt Lake City, Utah - Sustainability Solutions</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>Salt Lake City, Utah</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>https://stryker.wd1.myworkdayjobs.com/StrykerCareers/job/Salt-Lake-City-Utah/Service-Associate---Salt-Lake-City--Utah---Sustainability-Solutions_R575799</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
         <is>
           <t>Title: sustainability | LOCATION UNVERIFIED: Salt Lake City, Utah</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Airbus</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>A400M Fleet maintenance data analyst</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Getafe Area</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Getafe-Area/A400M-Fleet-maintenance-data-analyst_JR10448810-1</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>Title: data analyst | LOCATION UNVERIFIED: Getafe Area</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1075,20 +1075,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Stage 2027 - Stagiaire en Atténuation des effets non-CO2 de l'aviation (F/H)</t>
+          <t>A400M Fleet maintenance data analyst</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Toulouse Area</t>
+          <t>Getafe Area</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Toulouse-Area/Stage-2027---Stagiaire-en-Attnuation-des-effets-non-CO2-de-l-aviation--F-H-_JR10443593</t>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Getafe-Area/A400M-Fleet-maintenance-data-analyst_JR10448810-1</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1098,14 +1098,14 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Title: co2 | LOCATION UNVERIFIED: Toulouse Area</t>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Getafe Area</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Combat Business Planning and Reporting Analyst (Temp Agency)</t>
+          <t>Stage 2027 - Stagiaire en Atténuation des effets non-CO2 de l'aviation (F/H)</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1128,12 +1128,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Getafe Area</t>
+          <t>Toulouse Area</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Getafe-Area/Combat-Business-Planning-and-Reporting-Analyst--Temp-Agency-_JR10450246</t>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Toulouse-Area/Stage-2027---Stagiaire-en-Attnuation-des-effets-non-CO2-de-l-aviation--F-H-_JR10443593</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Title: reporting analyst | LOCATION UNVERIFIED: Getafe Area</t>
+          <t>Title: co2 | LOCATION UNVERIFIED: Toulouse Area</t>
         </is>
       </c>
     </row>
@@ -1165,20 +1165,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>STAGE 2027 - Data Analyste en qualité logistique (h/f)</t>
+          <t>Combat Business Planning and Reporting Analyst (Temp Agency)</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tremblay-en-France</t>
+          <t>Getafe Area</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Tremblay-en-France/STAGE-2027---Data-Analyste-en-qualit-logistique--h-f-_JR10443345</t>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Getafe-Area/Combat-Business-Planning-and-Reporting-Analyst--Temp-Agency-_JR10450246</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1188,14 +1188,14 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Title: data analyst | LOCATION UNVERIFIED: Tremblay-en-France</t>
+          <t>Title: reporting analyst | LOCATION UNVERIFIED: Getafe Area</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>STAGE 2027 - Finance Data Analyst (m/f)</t>
+          <t>STAGE 2027 - Data Analyste en qualité logistique (h/f)</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Marseille Area</t>
+          <t>Tremblay-en-France</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Marseille-Area/XMLNAME---Internship---Offer-Evaluation-digitalization---Finance-BI-Analyst--m-f--_JR10443902</t>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Tremblay-en-France/STAGE-2027---Data-Analyste-en-qualit-logistique--h-f-_JR10443345</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1233,19 +1233,19 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Title: data analyst | LOCATION UNVERIFIED: Marseille Area</t>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Tremblay-en-France</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sun Oct 25 02:00:00 UTC 2026</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>Airbus</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1255,15 +1255,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Systemingenieur für Radar Environmental Simulator (w/m/d)</t>
+          <t>STAGE 2027 - Finance Data Analyst (m/f)</t>
         </is>
       </c>
       <c r="E19" t="n">
         <v>2</v>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Marseille Area</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/Ulm-Systemingenieur-f%C3%BCr-Radar-Environmental-Simulator-%28wmd%29-89077/1365917055/</t>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Marseille-Area/XMLNAME---Internship---Offer-Evaluation-digitalization---Finance-BI-Analyst--m-f--_JR10443902</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1273,19 +1278,19 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Title: environmental | LOCATION UNVERIFIED: none</t>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Marseille Area</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>Sun Oct 25 02:00:00 UTC 2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Workday Munich</t>
+          <t>Hensoldt</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1295,28 +1300,68 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Reporting Analyst, Workday Reporting</t>
+          <t>Systemingenieur für Radar Environmental Simulator (w/m/d)</t>
         </is>
       </c>
       <c r="E20" t="n">
         <v>2</v>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/Ulm-Systemingenieur-f%C3%BCr-Radar-Environmental-Simulator-%28wmd%29-89077/1365917055/</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Title: environmental | LOCATION UNVERIFIED: none</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Workday Munich</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Reporting Analyst, Workday Reporting</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>IND.Pune</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>https://workday.wd5.myworkdayjobs.com/Workday/job/INDPune/Reporting-Analyst--Workday-Reporting_JR-0110733</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>Title: reporting analyst | LOCATION UNVERIFIED: IND.Pune</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -533,45 +533,45 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Tue Oct 27 02:00:00 UTC 2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>EY Germany</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>Manager - Climate Change and Sustainability Services</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" t="n">
         <v>10</v>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Sydney, NSW, AU, 2000 +5 more…</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://careers.ey.com/ey/job/Sydney-Manager-Climate-Change-and-Sustainability-Services-NSW-2000/1441652233/</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>Title: sustainability | LOCATION UNVERIFIED: Sydney, NSW, AU, 2000 +5 more…</t>
         </is>
@@ -580,7 +580,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -715,7 +715,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -760,7 +760,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -970,7 +970,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1015,7 +1015,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1150,7 +1150,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1195,7 +1195,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1240,7 +1240,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1325,7 +1325,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -580,7 +580,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -715,7 +715,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -760,7 +760,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -970,7 +970,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1015,7 +1015,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1060,7 +1060,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1103,54 +1103,54 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Airbus</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Stage 2027 - Stagiaire en Atténuation des effets non-CO2 de l'aviation (F/H)</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>3</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Toulouse Area</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Toulouse-Area/Stage-2027---Stagiaire-en-Attnuation-des-effets-non-CO2-de-l-aviation--F-H-_JR10443593</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Title: co2 | LOCATION UNVERIFIED: Toulouse Area</t>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Salesforce Munich</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Technical Data Analyst</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Mexico - Mexico City</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>https://salesforce.wd12.myworkdayjobs.com/External_Career_Site/job/Mexico---Mexico-City/System-Senior-Analyst_JR364924-1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Mexico - Mexico City</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Combat Business Planning and Reporting Analyst (Temp Agency)</t>
+          <t>Stage 2027 - Stagiaire en Atténuation des effets non-CO2 de l'aviation (F/H)</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1173,12 +1173,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Getafe Area</t>
+          <t>Toulouse Area</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Getafe-Area/Combat-Business-Planning-and-Reporting-Analyst--Temp-Agency-_JR10450246</t>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Toulouse-Area/Stage-2027---Stagiaire-en-Attnuation-des-effets-non-CO2-de-l-aviation--F-H-_JR10443593</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Title: reporting analyst | LOCATION UNVERIFIED: Getafe Area</t>
+          <t>Title: co2 | LOCATION UNVERIFIED: Toulouse Area</t>
         </is>
       </c>
     </row>
@@ -1210,20 +1210,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>STAGE 2027 - Data Analyste en qualité logistique (h/f)</t>
+          <t>Combat Business Planning and Reporting Analyst (Temp Agency)</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tremblay-en-France</t>
+          <t>Getafe Area</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Tremblay-en-France/STAGE-2027---Data-Analyste-en-qualit-logistique--h-f-_JR10443345</t>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Getafe-Area/Combat-Business-Planning-and-Reporting-Analyst--Temp-Agency-_JR10450246</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1233,14 +1233,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Title: data analyst | LOCATION UNVERIFIED: Tremblay-en-France</t>
+          <t>Title: reporting analyst | LOCATION UNVERIFIED: Getafe Area</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>STAGE 2027 - Finance Data Analyst (m/f)</t>
+          <t>STAGE 2027 - Data Analyste en qualité logistique (h/f)</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1263,12 +1263,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Marseille Area</t>
+          <t>Tremblay-en-France</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Marseille-Area/XMLNAME---Internship---Offer-Evaluation-digitalization---Finance-BI-Analyst--m-f--_JR10443902</t>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Tremblay-en-France/STAGE-2027---Data-Analyste-en-qualit-logistique--h-f-_JR10443345</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1278,19 +1278,19 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Title: data analyst | LOCATION UNVERIFIED: Marseille Area</t>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Tremblay-en-France</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sun Oct 25 02:00:00 UTC 2026</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>Airbus</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1300,15 +1300,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Systemingenieur für Radar Environmental Simulator (w/m/d)</t>
+          <t>STAGE 2027 - Finance Data Analyst (m/f)</t>
         </is>
       </c>
       <c r="E20" t="n">
         <v>2</v>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Marseille Area</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/Ulm-Systemingenieur-f%C3%BCr-Radar-Environmental-Simulator-%28wmd%29-89077/1365917055/</t>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Marseille-Area/XMLNAME---Internship---Offer-Evaluation-digitalization---Finance-BI-Analyst--m-f--_JR10443902</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1318,19 +1323,19 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Title: environmental | LOCATION UNVERIFIED: none</t>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Marseille Area</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>Sun Oct 25 02:00:00 UTC 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Workday Munich</t>
+          <t>Hensoldt</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1340,28 +1345,68 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Reporting Analyst, Workday Reporting</t>
+          <t>Systemingenieur für Radar Environmental Simulator (w/m/d)</t>
         </is>
       </c>
       <c r="E21" t="n">
         <v>2</v>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/Ulm-Systemingenieur-f%C3%BCr-Radar-Environmental-Simulator-%28wmd%29-89077/1365917055/</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Title: environmental | LOCATION UNVERIFIED: none</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Workday Munich</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Reporting Analyst, Workday Reporting</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>IND.Pune</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>https://workday.wd5.myworkdayjobs.com/Workday/job/INDPune/Reporting-Analyst--Workday-Reporting_JR-0110733</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>Title: reporting analyst | LOCATION UNVERIFIED: IND.Pune</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -580,7 +580,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -713,234 +713,249 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Bristol Myers Squibb Munich</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Manager, Environmental Health, Safety and Sustainability - Safety</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>San Diego - CA - US</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>https://bristolmyerssquibb.wd5.myworkdayjobs.com/BMS/job/San-Diego---CA---US/Manager--Environmental-Health--Safety-and-Sustainability---Safety_R1607841</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Title: sustainability | LOCATION UNVERIFIED: San Diego - CA - US</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Bristol Myers Squibb Munich</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Manager, Environmental Health, Safety and Sustainability – Environmental Compliance</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>San Diego - CA - US</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>https://bristolmyerssquibb.wd5.myworkdayjobs.com/BMS/job/San-Diego---CA---US/Manager--Environmental-Health--Safety-and-Sustainability---Environmental-Compliance_R1607843</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Title: sustainability | LOCATION UNVERIFIED: San Diego - CA - US</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Human Rights and Sustainability Compliance</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>https://accenture.wd103.myworkdayjobs.com/AccentureCareers/job/Bucharest/Human-Rights-and-Sustainability-Compliance_R00363151</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Title: sustainability | LOCATION UNVERIFIED: Bucharest</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>Airbus</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>Environmental Test Engineer</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E10" t="n">
         <v>5</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Stevenage</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Stevenage/Environmental-Test-Engineer_JR10408723</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>Title: environmental | LOCATION UNVERIFIED: Stevenage</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>Amgen Munich</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>Environmental Health &amp; Safety Manager</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E11" t="n">
         <v>5</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>US - California - South San Francisco</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>https://amgen.wd1.myworkdayjobs.com/Careers/job/US---California---South-San-Francisco/Environmental-Health---Safety-Manager_R-258423-1</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>Title: environmental | LOCATION UNVERIFIED: US - California - South San Francisco</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>Environmental Management Specialist (f/m/d)</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>4</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Parsdorf, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/5009977101</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Title: environmental</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>FlixMobility</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Commercial Data Analyst Mexico City Regular</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Mexico City</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://flix.careers/job/?jobid=8364246002</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Title: data analyst | LOCATION UNVERIFIED: Mexico City</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>FlixMobility</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Jr. Financial Planning &amp; Reporting Specialist (m/f/d) Sofia Regular</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>4</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Sofia</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://flix.careers/job/?jobid=8891299002</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Title: reporting specialist | LOCATION UNVERIFIED: Sofia</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>FlixMobility</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Jr. Financial Planning &amp; Reporting Specialist (m/f/d) Sofia Regular</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -948,12 +963,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sofia</t>
+          <t>Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://flix.careers/job/?jobid=8622257002</t>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/5009977101</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -963,19 +978,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Title: reporting specialist | LOCATION UNVERIFIED: Sofia</t>
+          <t>Title: environmental</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Stryker Munich</t>
+          <t>FlixMobility</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -985,7 +995,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Service Associate - Detroit, MI - Sustainability Solutions</t>
+          <t>Commercial Data Analyst Mexico City Regular</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -993,12 +1003,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Detroit, Michigan</t>
+          <t>Mexico City</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://stryker.wd1.myworkdayjobs.com/StrykerCareers/job/Detroit-Michigan/Service-Associate---Detroit--MI---Sustainability-Solutions_R576161</t>
+          <t>https://flix.careers/job/?jobid=8364246002</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1008,19 +1018,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Title: sustainability | LOCATION UNVERIFIED: Detroit, Michigan</t>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Mexico City</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Stryker Munich</t>
+          <t>FlixMobility</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1030,7 +1035,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Service Associate - Salt Lake City, Utah - Sustainability Solutions</t>
+          <t>Jr. Financial Planning &amp; Reporting Specialist (m/f/d) Sofia Regular</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1038,12 +1043,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Salt Lake City, Utah</t>
+          <t>Sofia</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://stryker.wd1.myworkdayjobs.com/StrykerCareers/job/Salt-Lake-City-Utah/Service-Associate---Salt-Lake-City--Utah---Sustainability-Solutions_R575799</t>
+          <t>https://flix.careers/job/?jobid=8891299002</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1053,19 +1058,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Title: sustainability | LOCATION UNVERIFIED: Salt Lake City, Utah</t>
+          <t>Title: reporting specialist | LOCATION UNVERIFIED: Sofia</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Airbus</t>
+          <t>FlixMobility</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>A400M Fleet maintenance data analyst</t>
+          <t>Jr. Financial Planning &amp; Reporting Specialist (m/f/d) Sofia Regular</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1083,12 +1083,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Getafe Area</t>
+          <t>Sofia</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Getafe-Area/A400M-Fleet-maintenance-data-analyst_JR10448810-1</t>
+          <t>https://flix.careers/job/?jobid=8622257002</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1098,64 +1098,64 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Title: data analyst | LOCATION UNVERIFIED: Getafe Area</t>
+          <t>Title: reporting specialist | LOCATION UNVERIFIED: Sofia</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Salesforce Munich</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Technical Data Analyst</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="n">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Stryker Munich</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Service Associate - Detroit, MI - Sustainability Solutions</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
         <v>4</v>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Mexico - Mexico City</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>https://salesforce.wd12.myworkdayjobs.com/External_Career_Site/job/Mexico---Mexico-City/System-Senior-Analyst_JR364924-1</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>Title: data analyst | LOCATION UNVERIFIED: Mexico - Mexico City</t>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Detroit, Michigan</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://stryker.wd1.myworkdayjobs.com/StrykerCareers/job/Detroit-Michigan/Service-Associate---Detroit--MI---Sustainability-Solutions_R576161</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Title: sustainability | LOCATION UNVERIFIED: Detroit, Michigan</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Airbus</t>
+          <t>Stryker Munich</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1165,20 +1165,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Stage 2027 - Stagiaire en Atténuation des effets non-CO2 de l'aviation (F/H)</t>
+          <t>Service Associate - Salt Lake City, Utah - Sustainability Solutions</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Toulouse Area</t>
+          <t>Salt Lake City, Utah</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Toulouse-Area/Stage-2027---Stagiaire-en-Attnuation-des-effets-non-CO2-de-l-aviation--F-H-_JR10443593</t>
+          <t>https://stryker.wd1.myworkdayjobs.com/StrykerCareers/job/Salt-Lake-City-Utah/Service-Associate---Salt-Lake-City--Utah---Sustainability-Solutions_R575799</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1188,14 +1188,14 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Title: co2 | LOCATION UNVERIFIED: Toulouse Area</t>
+          <t>Title: sustainability | LOCATION UNVERIFIED: Salt Lake City, Utah</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1210,11 +1210,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Combat Business Planning and Reporting Analyst (Temp Agency)</t>
+          <t>A400M Fleet maintenance data analyst</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Getafe-Area/Combat-Business-Planning-and-Reporting-Analyst--Temp-Agency-_JR10450246</t>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Getafe-Area/A400M-Fleet-maintenance-data-analyst_JR10448810-1</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1233,19 +1233,19 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Title: reporting analyst | LOCATION UNVERIFIED: Getafe Area</t>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Getafe Area</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Airbus</t>
+          <t>Salesforce Munich</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1255,20 +1255,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>STAGE 2027 - Data Analyste en qualité logistique (h/f)</t>
+          <t>Technical Data Analyst</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tremblay-en-France</t>
+          <t>Mexico - Mexico City</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Tremblay-en-France/STAGE-2027---Data-Analyste-en-qualit-logistique--h-f-_JR10443345</t>
+          <t>https://salesforce.wd12.myworkdayjobs.com/External_Career_Site/job/Mexico---Mexico-City/System-Senior-Analyst_JR364924-1</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1278,14 +1278,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Title: data analyst | LOCATION UNVERIFIED: Tremblay-en-France</t>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Mexico - Mexico City</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1300,20 +1300,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>STAGE 2027 - Finance Data Analyst (m/f)</t>
+          <t>Stage 2027 - Stagiaire en Atténuation des effets non-CO2 de l'aviation (F/H)</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Marseille Area</t>
+          <t>Toulouse Area</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Marseille-Area/XMLNAME---Internship---Offer-Evaluation-digitalization---Finance-BI-Analyst--m-f--_JR10443902</t>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Toulouse-Area/Stage-2027---Stagiaire-en-Attnuation-des-effets-non-CO2-de-l-aviation--F-H-_JR10443593</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1323,19 +1323,19 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Title: data analyst | LOCATION UNVERIFIED: Marseille Area</t>
+          <t>Title: co2 | LOCATION UNVERIFIED: Toulouse Area</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sun Oct 25 02:00:00 UTC 2026</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>Airbus</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1345,15 +1345,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Systemingenieur für Radar Environmental Simulator (w/m/d)</t>
+          <t>Combat Business Planning and Reporting Analyst (Temp Agency)</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Getafe Area</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/Ulm-Systemingenieur-f%C3%BCr-Radar-Environmental-Simulator-%28wmd%29-89077/1365917055/</t>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Getafe-Area/Combat-Business-Planning-and-Reporting-Analyst--Temp-Agency-_JR10450246</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1363,19 +1368,19 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Title: environmental | LOCATION UNVERIFIED: none</t>
+          <t>Title: reporting analyst | LOCATION UNVERIFIED: Getafe Area</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Workday Munich</t>
+          <t>Airbus</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1385,7 +1390,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Reporting Analyst, Workday Reporting</t>
+          <t>STAGE 2027 - Data Analyste en qualité logistique (h/f)</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1393,20 +1398,150 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>Tremblay-en-France</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Tremblay-en-France/STAGE-2027---Data-Analyste-en-qualit-logistique--h-f-_JR10443345</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Tremblay-en-France</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>STAGE 2027 - Finance Data Analyst (m/f)</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Marseille Area</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Marseille-Area/XMLNAME---Internship---Offer-Evaluation-digitalization---Finance-BI-Analyst--m-f--_JR10443902</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Marseille Area</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Sun Oct 25 02:00:00 UTC 2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Systemingenieur für Radar Environmental Simulator (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/Ulm-Systemingenieur-f%C3%BCr-Radar-Environmental-Simulator-%28wmd%29-89077/1365917055/</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Title: environmental | LOCATION UNVERIFIED: none</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Workday Munich</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Reporting Analyst, Workday Reporting</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>IND.Pune</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>https://workday.wd5.myworkdayjobs.com/Workday/job/INDPune/Reporting-Analyst--Workday-Reporting_JR-0110733</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>Title: reporting analyst | LOCATION UNVERIFIED: IND.Pune</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -580,7 +580,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -713,135 +713,135 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>Bristol Myers Squibb Munich</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>Manager, Environmental Health, Safety and Sustainability - Safety</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" t="n">
         <v>8</v>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>San Diego - CA - US</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://bristolmyerssquibb.wd5.myworkdayjobs.com/BMS/job/San-Diego---CA---US/Manager--Environmental-Health--Safety-and-Sustainability---Safety_R1607841</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>Title: sustainability | LOCATION UNVERIFIED: San Diego - CA - US</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>Bristol Myers Squibb Munich</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>Manager, Environmental Health, Safety and Sustainability – Environmental Compliance</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" t="n">
         <v>7</v>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>San Diego - CA - US</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://bristolmyerssquibb.wd5.myworkdayjobs.com/BMS/job/San-Diego---CA---US/Manager--Environmental-Health--Safety-and-Sustainability---Environmental-Compliance_R1607843</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>Title: sustainability | LOCATION UNVERIFIED: San Diego - CA - US</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>Accenture</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>Human Rights and Sustainability Compliance</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" t="n">
         <v>7</v>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Bucharest</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://accenture.wd103.myworkdayjobs.com/AccentureCareers/job/Bucharest/Human-Rights-and-Sustainability-Compliance_R00363151</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>Title: sustainability | LOCATION UNVERIFIED: Bucharest</t>
         </is>
@@ -895,7 +895,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1195,7 +1195,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1240,7 +1240,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1330,7 +1330,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1375,7 +1375,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1420,7 +1420,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1505,7 +1505,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -580,7 +580,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -715,7 +715,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -760,7 +760,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -805,7 +805,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -848,59 +848,59 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Airbus</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Environmental Test Engineer</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>5</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Stevenage</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Stevenage/Environmental-Test-Engineer_JR10408723</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Title: environmental | LOCATION UNVERIFIED: Stevenage</t>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Infineon Technologies</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>HR Data Analyst Trainee (f/m/div)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Porto, Porto District,PT</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.infineon.com/careers/job/563808972279882</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Porto, Porto District,PT</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Amgen Munich</t>
+          <t>Airbus</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Environmental Health &amp; Safety Manager</t>
+          <t>Environmental Test Engineer</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -918,12 +918,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>US - California - South San Francisco</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://amgen.wd1.myworkdayjobs.com/Careers/job/US---California---South-San-Francisco/Environmental-Health---Safety-Manager_R-258423-1</t>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Stevenage/Environmental-Test-Engineer_JR10408723</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Title: environmental | LOCATION UNVERIFIED: US - California - South San Francisco</t>
+          <t>Title: environmental | LOCATION UNVERIFIED: Stevenage</t>
         </is>
       </c>
     </row>
@@ -945,57 +945,62 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>Amgen Munich</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Environmental Health &amp; Safety Manager</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>US - California - South San Francisco</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://amgen.wd1.myworkdayjobs.com/Careers/job/US---California---South-San-Francisco/Environmental-Health---Safety-Manager_R-258423-1</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Title: environmental | LOCATION UNVERIFIED: US - California - South San Francisco</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>Environmental Management Specialist (f/m/d)</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>4</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Parsdorf, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/5009977101</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Title: environmental</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>FlixMobility</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Commercial Data Analyst Mexico City Regular</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1003,12 +1008,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mexico City</t>
+          <t>Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://flix.careers/job/?jobid=8364246002</t>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/5009977101</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1018,7 +1023,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Title: data analyst | LOCATION UNVERIFIED: Mexico City</t>
+          <t>Title: environmental</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1040,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Jr. Financial Planning &amp; Reporting Specialist (m/f/d) Sofia Regular</t>
+          <t>Commercial Data Analyst Mexico City Regular</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1043,12 +1048,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sofia</t>
+          <t>Mexico City</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://flix.careers/job/?jobid=8891299002</t>
+          <t>https://flix.careers/job/?jobid=8364246002</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1058,7 +1063,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Title: reporting specialist | LOCATION UNVERIFIED: Sofia</t>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Mexico City</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1093,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://flix.careers/job/?jobid=8622257002</t>
+          <t>https://flix.careers/job/?jobid=8891299002</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1103,14 +1108,9 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Stryker Munich</t>
+          <t>FlixMobility</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Service Associate - Detroit, MI - Sustainability Solutions</t>
+          <t>Jr. Financial Planning &amp; Reporting Specialist (m/f/d) Sofia Regular</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1128,12 +1128,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Detroit, Michigan</t>
+          <t>Sofia</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://stryker.wd1.myworkdayjobs.com/StrykerCareers/job/Detroit-Michigan/Service-Associate---Detroit--MI---Sustainability-Solutions_R576161</t>
+          <t>https://flix.careers/job/?jobid=8622257002</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1143,14 +1143,14 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Title: sustainability | LOCATION UNVERIFIED: Detroit, Michigan</t>
+          <t>Title: reporting specialist | LOCATION UNVERIFIED: Sofia</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Service Associate - Salt Lake City, Utah - Sustainability Solutions</t>
+          <t>Service Associate - Detroit, MI - Sustainability Solutions</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1173,12 +1173,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Salt Lake City, Utah</t>
+          <t>Detroit, Michigan</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://stryker.wd1.myworkdayjobs.com/StrykerCareers/job/Salt-Lake-City-Utah/Service-Associate---Salt-Lake-City--Utah---Sustainability-Solutions_R575799</t>
+          <t>https://stryker.wd1.myworkdayjobs.com/StrykerCareers/job/Detroit-Michigan/Service-Associate---Detroit--MI---Sustainability-Solutions_R576161</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1188,19 +1188,19 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Title: sustainability | LOCATION UNVERIFIED: Salt Lake City, Utah</t>
+          <t>Title: sustainability | LOCATION UNVERIFIED: Detroit, Michigan</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Airbus</t>
+          <t>Stryker Munich</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>A400M Fleet maintenance data analyst</t>
+          <t>Service Associate - Salt Lake City, Utah - Sustainability Solutions</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Getafe Area</t>
+          <t>Salt Lake City, Utah</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Getafe-Area/A400M-Fleet-maintenance-data-analyst_JR10448810-1</t>
+          <t>https://stryker.wd1.myworkdayjobs.com/StrykerCareers/job/Salt-Lake-City-Utah/Service-Associate---Salt-Lake-City--Utah---Sustainability-Solutions_R575799</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1233,19 +1233,19 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Title: data analyst | LOCATION UNVERIFIED: Getafe Area</t>
+          <t>Title: sustainability | LOCATION UNVERIFIED: Salt Lake City, Utah</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Salesforce Munich</t>
+          <t>Airbus</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Technical Data Analyst</t>
+          <t>A400M Fleet maintenance data analyst</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1263,12 +1263,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mexico - Mexico City</t>
+          <t>Getafe Area</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://salesforce.wd12.myworkdayjobs.com/External_Career_Site/job/Mexico---Mexico-City/System-Senior-Analyst_JR364924-1</t>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Getafe-Area/A400M-Fleet-maintenance-data-analyst_JR10448810-1</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1278,19 +1278,19 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Title: data analyst | LOCATION UNVERIFIED: Mexico - Mexico City</t>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Getafe Area</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Airbus</t>
+          <t>Salesforce Munich</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1300,20 +1300,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Stage 2027 - Stagiaire en Atténuation des effets non-CO2 de l'aviation (F/H)</t>
+          <t>Technical Data Analyst</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Toulouse Area</t>
+          <t>Mexico - Mexico City</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Toulouse-Area/Stage-2027---Stagiaire-en-Attnuation-des-effets-non-CO2-de-l-aviation--F-H-_JR10443593</t>
+          <t>https://salesforce.wd12.myworkdayjobs.com/External_Career_Site/job/Mexico---Mexico-City/System-Senior-Analyst_JR364924-1</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Title: co2 | LOCATION UNVERIFIED: Toulouse Area</t>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Mexico - Mexico City</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Combat Business Planning and Reporting Analyst (Temp Agency)</t>
+          <t>Stage 2027 - Stagiaire en Atténuation des effets non-CO2 de l'aviation (F/H)</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Getafe Area</t>
+          <t>Toulouse Area</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Getafe-Area/Combat-Business-Planning-and-Reporting-Analyst--Temp-Agency-_JR10450246</t>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Toulouse-Area/Stage-2027---Stagiaire-en-Attnuation-des-effets-non-CO2-de-l-aviation--F-H-_JR10443593</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1368,109 +1368,109 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Title: reporting analyst | LOCATION UNVERIFIED: Getafe Area</t>
+          <t>Title: co2 | LOCATION UNVERIFIED: Toulouse Area</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Combat Business Planning and Reporting Analyst (Temp Agency)</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Getafe Area</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Getafe-Area/Combat-Business-Planning-and-Reporting-Analyst--Temp-Agency-_JR10450246</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Title: reporting analyst | LOCATION UNVERIFIED: Getafe Area</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Airbus</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>STAGE 2027 - Data Analyste en qualité logistique (h/f)</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>2</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Tremblay-en-France</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Tremblay-en-France/STAGE-2027---Data-Analyste-en-qualit-logistique--h-f-_JR10443345</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Title: data analyst | LOCATION UNVERIFIED: Tremblay-en-France</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Airbus</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>STAGE 2027 - Finance Data Analyst (m/f)</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>2</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Marseille Area</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Marseille-Area/XMLNAME---Internship---Offer-Evaluation-digitalization---Finance-BI-Analyst--m-f--_JR10443902</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Title: data analyst | LOCATION UNVERIFIED: Marseille Area</t>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Stage 2027- Data Analyst &amp; AI - Corporate Audit (h/f)</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Toulouse Area</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Toulouse-Area/Stage-2027--Data-Analyst---AI---Corporate-Audit--h-f-_JR10445497</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Toulouse Area</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sun Oct 25 02:00:00 UTC 2026</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>Airbus</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1480,15 +1480,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Systemingenieur für Radar Environmental Simulator (w/m/d)</t>
+          <t>STAGE 2027 - Data Analyste en qualité logistique (h/f)</t>
         </is>
       </c>
       <c r="E24" t="n">
         <v>2</v>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tremblay-en-France</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/Ulm-Systemingenieur-f%C3%BCr-Radar-Environmental-Simulator-%28wmd%29-89077/1365917055/</t>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Tremblay-en-France/STAGE-2027---Data-Analyste-en-qualit-logistique--h-f-_JR10443345</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1498,19 +1503,19 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Title: environmental | LOCATION UNVERIFIED: none</t>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Tremblay-en-France</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Workday Munich</t>
+          <t>Airbus</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1520,7 +1525,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Reporting Analyst, Workday Reporting</t>
+          <t>STAGE 2027 - Finance Data Analyst (m/f)</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1528,20 +1533,105 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
+          <t>Marseille Area</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Marseille-Area/XMLNAME---Internship---Offer-Evaluation-digitalization---Finance-BI-Analyst--m-f--_JR10443902</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Marseille Area</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Sun Oct 25 02:00:00 UTC 2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Systemingenieur für Radar Environmental Simulator (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/Ulm-Systemingenieur-f%C3%BCr-Radar-Environmental-Simulator-%28wmd%29-89077/1365917055/</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Title: environmental | LOCATION UNVERIFIED: none</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Workday Munich</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Reporting Analyst, Workday Reporting</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>IND.Pune</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>https://workday.wd5.myworkdayjobs.com/Workday/job/INDPune/Reporting-Analyst--Workday-Reporting_JR-0110733</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>Title: reporting analyst | LOCATION UNVERIFIED: IND.Pune</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -580,7 +580,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -715,7 +715,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -760,7 +760,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -805,7 +805,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -848,45 +848,45 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Infineon Technologies</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>HR Data Analyst Trainee (f/m/div)</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" t="n">
         <v>6</v>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Porto, Porto District,PT</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://jobs.infineon.com/careers/job/563808972279882</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>Title: data analyst | LOCATION UNVERIFIED: Porto, Porto District,PT</t>
         </is>
@@ -895,7 +895,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -940,7 +940,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1150,7 +1150,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1195,7 +1195,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1240,7 +1240,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1285,7 +1285,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1375,7 +1375,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1418,45 +1418,45 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
         <is>
           <t>Airbus</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>Stage 2027- Data Analyst &amp; AI - Corporate Audit (h/f)</t>
         </is>
       </c>
-      <c r="E23" s="2" t="n">
+      <c r="E23" t="n">
         <v>3</v>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Toulouse Area</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Toulouse-Area/Stage-2027--Data-Analyst---AI---Corporate-Audit--h-f-_JR10445497</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>Title: data analyst | LOCATION UNVERIFIED: Toulouse Area</t>
         </is>
@@ -1465,7 +1465,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1510,7 +1510,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1595,7 +1595,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -533,59 +533,55 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Tue Oct 27 02:00:00 UTC 2026</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>EY Germany</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Manager - Climate Change and Sustainability Services</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Sydney, NSW, AU, 2000 +5 more…</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://careers.ey.com/ey/job/Sydney-Manager-Climate-Change-and-Sustainability-Services-NSW-2000/1441652233/</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Title: sustainability | LOCATION UNVERIFIED: Sydney, NSW, AU, 2000 +5 more…</t>
+      <c r="A3" s="2" t="inlineStr"/>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Westwing</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Data Analyst (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Munich Office</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>https://westwing.jobs.personio.de/job/2860526</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Title: data analyst</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>Tue Oct 27 02:00:00 UTC 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Airbus</t>
+          <t>EY Germany</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -595,20 +591,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Procurement Data Analyst</t>
+          <t>Manager - Climate Change and Sustainability Services</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lisbon (Airbus Portugal); Coimbra</t>
+          <t>Sydney, NSW, AU, 2000 +5 more…</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Lisbon-Airbus-Portugal/Procurement-Data-Analyst_JR10446958</t>
+          <t>https://careers.ey.com/ey/job/Sydney-Manager-Climate-Change-and-Sustainability-Services-NSW-2000/1441652233/</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -618,14 +614,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Title: data analyst | LOCATION UNVERIFIED: Lisbon (Airbus Portugal); Coimbra</t>
+          <t>Title: sustainability | LOCATION UNVERIFIED: Sydney, NSW, AU, 2000 +5 more…</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -640,7 +636,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>STAGE 2027 - Scénarios prospectifs pour l'aviation : analyse énergétique et décarbonation (F/H)</t>
+          <t>Procurement Data Analyst</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -648,12 +644,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Toulouse Area</t>
+          <t>Lisbon (Airbus Portugal); Coimbra</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Toulouse-Area/STAGE-2027---Scnarios-prospectifs-pour-l-aviation---analyse-nergtique-et-dcarbonation--F-H-_JR10443850</t>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Lisbon-Airbus-Portugal/Procurement-Data-Analyst_JR10446958</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -663,19 +659,19 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Title: carbon | LOCATION UNVERIFIED: Toulouse Area</t>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Lisbon (Airbus Portugal); Coimbra</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Siemens Energy</t>
+          <t>Airbus</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -685,7 +681,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Data Analyst im Bereich Manufacturing (m/w/d)</t>
+          <t>STAGE 2027 - Scénarios prospectifs pour l'aviation : analyse énergétique et décarbonation (F/H)</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -693,12 +689,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Toulouse Area</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Data-Analyst-im-Bereich-Manufacturing-m-w-d/305767</t>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Toulouse-Area/STAGE-2027---Scnarios-prospectifs-pour-l-aviation---analyse-nergtique-et-dcarbonation--F-H-_JR10443850</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -708,19 +704,19 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Title: data analyst | LOCATION UNVERIFIED: Germany</t>
+          <t>Title: carbon | LOCATION UNVERIFIED: Toulouse Area</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb Munich</t>
+          <t>Siemens Energy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -730,7 +726,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Manager, Environmental Health, Safety and Sustainability - Safety</t>
+          <t>Data Analyst im Bereich Manufacturing (m/w/d)</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -738,12 +734,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>San Diego - CA - US</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://bristolmyerssquibb.wd5.myworkdayjobs.com/BMS/job/San-Diego---CA---US/Manager--Environmental-Health--Safety-and-Sustainability---Safety_R1607841</t>
+          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Data-Analyst-im-Bereich-Manufacturing-m-w-d/305767</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -753,14 +749,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Title: sustainability | LOCATION UNVERIFIED: San Diego - CA - US</t>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Germany</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -775,11 +771,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Manager, Environmental Health, Safety and Sustainability – Environmental Compliance</t>
+          <t>Manager, Environmental Health, Safety and Sustainability - Safety</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -788,7 +784,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://bristolmyerssquibb.wd5.myworkdayjobs.com/BMS/job/San-Diego---CA---US/Manager--Environmental-Health--Safety-and-Sustainability---Environmental-Compliance_R1607843</t>
+          <t>https://bristolmyerssquibb.wd5.myworkdayjobs.com/BMS/job/San-Diego---CA---US/Manager--Environmental-Health--Safety-and-Sustainability---Safety_R1607841</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -805,12 +801,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Bristol Myers Squibb Munich</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -820,7 +816,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Human Rights and Sustainability Compliance</t>
+          <t>Manager, Environmental Health, Safety and Sustainability – Environmental Compliance</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -828,12 +824,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bucharest</t>
+          <t>San Diego - CA - US</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://accenture.wd103.myworkdayjobs.com/AccentureCareers/job/Bucharest/Human-Rights-and-Sustainability-Compliance_R00363151</t>
+          <t>https://bristolmyerssquibb.wd5.myworkdayjobs.com/BMS/job/San-Diego---CA---US/Manager--Environmental-Health--Safety-and-Sustainability---Environmental-Compliance_R1607843</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -843,19 +839,19 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Title: sustainability | LOCATION UNVERIFIED: Bucharest</t>
+          <t>Title: sustainability | LOCATION UNVERIFIED: San Diego - CA - US</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Infineon Technologies</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -865,20 +861,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HR Data Analyst Trainee (f/m/div)</t>
+          <t>Human Rights and Sustainability Compliance</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Porto, Porto District,PT</t>
+          <t>Bucharest</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://jobs.infineon.com/careers/job/563808972279882</t>
+          <t>https://accenture.wd103.myworkdayjobs.com/AccentureCareers/job/Bucharest/Human-Rights-and-Sustainability-Compliance_R00363151</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -888,19 +884,19 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Title: data analyst | LOCATION UNVERIFIED: Porto, Porto District,PT</t>
+          <t>Title: sustainability | LOCATION UNVERIFIED: Bucharest</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Airbus</t>
+          <t>Infineon Technologies</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -910,20 +906,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Environmental Test Engineer</t>
+          <t>HR Data Analyst Trainee (f/m/div)</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Porto, Porto District,PT</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Stevenage/Environmental-Test-Engineer_JR10408723</t>
+          <t>https://jobs.infineon.com/careers/job/563808972279882</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -933,19 +929,19 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Title: environmental | LOCATION UNVERIFIED: Stevenage</t>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Porto, Porto District,PT</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Amgen Munich</t>
+          <t>Airbus</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -955,7 +951,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Environmental Health &amp; Safety Manager</t>
+          <t>Environmental Test Engineer</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -963,12 +959,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>US - California - South San Francisco</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://amgen.wd1.myworkdayjobs.com/Careers/job/US---California---South-San-Francisco/Environmental-Health---Safety-Manager_R-258423-1</t>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Stevenage/Environmental-Test-Engineer_JR10408723</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -978,7 +974,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Title: environmental | LOCATION UNVERIFIED: US - California - South San Francisco</t>
+          <t>Title: environmental | LOCATION UNVERIFIED: Stevenage</t>
         </is>
       </c>
     </row>
@@ -990,57 +986,62 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>Amgen Munich</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Environmental Health &amp; Safety Manager</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>US - California - South San Francisco</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://amgen.wd1.myworkdayjobs.com/Careers/job/US---California---South-San-Francisco/Environmental-Health---Safety-Manager_R-258423-1</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Title: environmental | LOCATION UNVERIFIED: US - California - South San Francisco</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>Environmental Management Specialist (f/m/d)</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>4</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Parsdorf, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/5009977101</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Title: environmental</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>FlixMobility</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Commercial Data Analyst Mexico City Regular</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1048,12 +1049,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mexico City</t>
+          <t>Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://flix.careers/job/?jobid=8364246002</t>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/5009977101</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1063,7 +1064,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Title: data analyst | LOCATION UNVERIFIED: Mexico City</t>
+          <t>Title: environmental</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1081,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Jr. Financial Planning &amp; Reporting Specialist (m/f/d) Sofia Regular</t>
+          <t>Commercial Data Analyst Mexico City Regular</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1088,12 +1089,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sofia</t>
+          <t>Mexico City</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://flix.careers/job/?jobid=8891299002</t>
+          <t>https://flix.careers/job/?jobid=8364246002</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1103,7 +1104,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Title: reporting specialist | LOCATION UNVERIFIED: Sofia</t>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Mexico City</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1134,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://flix.careers/job/?jobid=8622257002</t>
+          <t>https://flix.careers/job/?jobid=8891299002</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1148,14 +1149,9 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Stryker Munich</t>
+          <t>FlixMobility</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1165,7 +1161,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Service Associate - Detroit, MI - Sustainability Solutions</t>
+          <t>Jr. Financial Planning &amp; Reporting Specialist (m/f/d) Sofia Regular</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1173,12 +1169,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Detroit, Michigan</t>
+          <t>Sofia</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://stryker.wd1.myworkdayjobs.com/StrykerCareers/job/Detroit-Michigan/Service-Associate---Detroit--MI---Sustainability-Solutions_R576161</t>
+          <t>https://flix.careers/job/?jobid=8622257002</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1188,14 +1184,14 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Title: sustainability | LOCATION UNVERIFIED: Detroit, Michigan</t>
+          <t>Title: reporting specialist | LOCATION UNVERIFIED: Sofia</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1210,7 +1206,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Service Associate - Salt Lake City, Utah - Sustainability Solutions</t>
+          <t>Service Associate - Detroit, MI - Sustainability Solutions</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1218,12 +1214,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Salt Lake City, Utah</t>
+          <t>Detroit, Michigan</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://stryker.wd1.myworkdayjobs.com/StrykerCareers/job/Salt-Lake-City-Utah/Service-Associate---Salt-Lake-City--Utah---Sustainability-Solutions_R575799</t>
+          <t>https://stryker.wd1.myworkdayjobs.com/StrykerCareers/job/Detroit-Michigan/Service-Associate---Detroit--MI---Sustainability-Solutions_R576161</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1233,19 +1229,19 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Title: sustainability | LOCATION UNVERIFIED: Salt Lake City, Utah</t>
+          <t>Title: sustainability | LOCATION UNVERIFIED: Detroit, Michigan</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Airbus</t>
+          <t>Stryker Munich</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1255,7 +1251,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>A400M Fleet maintenance data analyst</t>
+          <t>Service Associate - Salt Lake City, Utah - Sustainability Solutions</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1263,12 +1259,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Getafe Area</t>
+          <t>Salt Lake City, Utah</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Getafe-Area/A400M-Fleet-maintenance-data-analyst_JR10448810-1</t>
+          <t>https://stryker.wd1.myworkdayjobs.com/StrykerCareers/job/Salt-Lake-City-Utah/Service-Associate---Salt-Lake-City--Utah---Sustainability-Solutions_R575799</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1278,19 +1274,19 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Title: data analyst | LOCATION UNVERIFIED: Getafe Area</t>
+          <t>Title: sustainability | LOCATION UNVERIFIED: Salt Lake City, Utah</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Salesforce Munich</t>
+          <t>Airbus</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1300,7 +1296,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Technical Data Analyst</t>
+          <t>A400M Fleet maintenance data analyst</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1308,12 +1304,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mexico - Mexico City</t>
+          <t>Getafe Area</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://salesforce.wd12.myworkdayjobs.com/External_Career_Site/job/Mexico---Mexico-City/System-Senior-Analyst_JR364924-1</t>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Getafe-Area/A400M-Fleet-maintenance-data-analyst_JR10448810-1</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1323,19 +1319,19 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Title: data analyst | LOCATION UNVERIFIED: Mexico - Mexico City</t>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Getafe Area</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Airbus</t>
+          <t>Salesforce Munich</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1345,20 +1341,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Stage 2027 - Stagiaire en Atténuation des effets non-CO2 de l'aviation (F/H)</t>
+          <t>Technical Data Analyst</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Toulouse Area</t>
+          <t>Mexico - Mexico City</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Toulouse-Area/Stage-2027---Stagiaire-en-Attnuation-des-effets-non-CO2-de-l-aviation--F-H-_JR10443593</t>
+          <t>https://salesforce.wd12.myworkdayjobs.com/External_Career_Site/job/Mexico---Mexico-City/System-Senior-Analyst_JR364924-1</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1368,7 +1364,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Title: co2 | LOCATION UNVERIFIED: Toulouse Area</t>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Mexico - Mexico City</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1386,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Combat Business Planning and Reporting Analyst (Temp Agency)</t>
+          <t>Stage 2027 - Stagiaire en Atténuation des effets non-CO2 de l'aviation (F/H)</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1398,12 +1394,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Getafe Area</t>
+          <t>Toulouse Area</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Getafe-Area/Combat-Business-Planning-and-Reporting-Analyst--Temp-Agency-_JR10450246</t>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Toulouse-Area/Stage-2027---Stagiaire-en-Attnuation-des-effets-non-CO2-de-l-aviation--F-H-_JR10443593</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1413,14 +1409,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Title: reporting analyst | LOCATION UNVERIFIED: Getafe Area</t>
+          <t>Title: co2 | LOCATION UNVERIFIED: Toulouse Area</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1435,7 +1431,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Stage 2027- Data Analyst &amp; AI - Corporate Audit (h/f)</t>
+          <t>Combat Business Planning and Reporting Analyst (Temp Agency)</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1443,12 +1439,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Toulouse Area</t>
+          <t>Getafe Area</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Toulouse-Area/Stage-2027--Data-Analyst---AI---Corporate-Audit--h-f-_JR10445497</t>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Getafe-Area/Combat-Business-Planning-and-Reporting-Analyst--Temp-Agency-_JR10450246</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1458,7 +1454,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Title: data analyst | LOCATION UNVERIFIED: Toulouse Area</t>
+          <t>Title: reporting analyst | LOCATION UNVERIFIED: Getafe Area</t>
         </is>
       </c>
     </row>
@@ -1480,20 +1476,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>STAGE 2027 - Data Analyste en qualité logistique (h/f)</t>
+          <t>Stage 2027- Data Analyst &amp; AI - Corporate Audit (h/f)</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tremblay-en-France</t>
+          <t>Toulouse Area</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Tremblay-en-France/STAGE-2027---Data-Analyste-en-qualit-logistique--h-f-_JR10443345</t>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Toulouse-Area/Stage-2027--Data-Analyst---AI---Corporate-Audit--h-f-_JR10445497</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1503,64 +1499,64 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Title: data analyst | LOCATION UNVERIFIED: Tremblay-en-France</t>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Toulouse Area</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Airbus</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>STAGE 2027 - Finance Data Analyst (m/f)</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>2</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Marseille Area</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Marseille-Area/XMLNAME---Internship---Offer-Evaluation-digitalization---Finance-BI-Analyst--m-f--_JR10443902</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Title: data analyst | LOCATION UNVERIFIED: Marseille Area</t>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Stryker Munich</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Environmental, Health &amp; Safety Manager (Onsite)</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Tijuana, Mexico</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>https://stryker.wd1.myworkdayjobs.com/StrykerCareers/job/Tijuana-Mexico/Environmental--Health---Safety-Manager-_R564100</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Title: environmental | LOCATION UNVERIFIED: Tijuana, Mexico</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sun Oct 25 02:00:00 UTC 2026</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>Airbus</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1570,15 +1566,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Systemingenieur für Radar Environmental Simulator (w/m/d)</t>
+          <t>STAGE 2027 - Data Analyste en qualité logistique (h/f)</t>
         </is>
       </c>
       <c r="E26" t="n">
         <v>2</v>
       </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tremblay-en-France</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/Ulm-Systemingenieur-f%C3%BCr-Radar-Environmental-Simulator-%28wmd%29-89077/1365917055/</t>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Tremblay-en-France/STAGE-2027---Data-Analyste-en-qualit-logistique--h-f-_JR10443345</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1588,19 +1589,19 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Title: environmental | LOCATION UNVERIFIED: none</t>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Tremblay-en-France</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Workday Munich</t>
+          <t>Airbus</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1610,7 +1611,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Reporting Analyst, Workday Reporting</t>
+          <t>STAGE 2027 - Finance Data Analyst (m/f)</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1618,20 +1619,105 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
+          <t>Marseille Area</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Marseille-Area/XMLNAME---Internship---Offer-Evaluation-digitalization---Finance-BI-Analyst--m-f--_JR10443902</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Marseille Area</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Sun Oct 25 02:00:00 UTC 2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Systemingenieur für Radar Environmental Simulator (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/Ulm-Systemingenieur-f%C3%BCr-Radar-Environmental-Simulator-%28wmd%29-89077/1365917055/</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Title: environmental | LOCATION UNVERIFIED: none</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Workday Munich</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Reporting Analyst, Workday Reporting</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t>IND.Pune</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>https://workday.wd5.myworkdayjobs.com/Workday/job/INDPune/Reporting-Analyst--Workday-Reporting_JR-0110733</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
         <is>
           <t>Title: reporting analyst | LOCATION UNVERIFIED: IND.Pune</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -533,41 +533,40 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr"/>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Westwing</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>Commercial Data Analyst (m/f/d)</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" t="n">
         <v>4</v>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Munich Office</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://westwing.jobs.personio.de/job/2860526</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>Title: data analyst</t>
         </is>
@@ -619,54 +618,54 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Airbus</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Procurement Data Analyst</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Lisbon (Airbus Portugal); Coimbra</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Lisbon-Airbus-Portugal/Procurement-Data-Analyst_JR10446958</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Title: data analyst | LOCATION UNVERIFIED: Lisbon (Airbus Portugal); Coimbra</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Sat Oct 31 02:01:00 UTC 2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>EY Germany</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Forward Deployed Data and AI Business Analyst</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Warszawa, PL, 00-124 +5 more…</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.ey.com/ey/job/Warszawa-Forward-Deployed-Data-and-AI-Business-Analyst-00-124/1443899933/</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Related role</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Responsibilities: ghg_accounting, data_methodology, stakeholders | LOCATION UNVERIFIED: Warszawa, PL, 00-124 +5 more…</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -681,7 +680,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>STAGE 2027 - Scénarios prospectifs pour l'aviation : analyse énergétique et décarbonation (F/H)</t>
+          <t>Procurement Data Analyst</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -689,12 +688,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Toulouse Area</t>
+          <t>Lisbon (Airbus Portugal); Coimbra</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Toulouse-Area/STAGE-2027---Scnarios-prospectifs-pour-l-aviation---analyse-nergtique-et-dcarbonation--F-H-_JR10443850</t>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Lisbon-Airbus-Portugal/Procurement-Data-Analyst_JR10446958</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -704,19 +703,19 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Title: carbon | LOCATION UNVERIFIED: Toulouse Area</t>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Lisbon (Airbus Portugal); Coimbra</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Siemens Energy</t>
+          <t>Airbus</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -726,7 +725,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Data Analyst im Bereich Manufacturing (m/w/d)</t>
+          <t>STAGE 2027 - Scénarios prospectifs pour l'aviation : analyse énergétique et décarbonation (F/H)</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -734,12 +733,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Toulouse Area</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Data-Analyst-im-Bereich-Manufacturing-m-w-d/305767</t>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Toulouse-Area/STAGE-2027---Scnarios-prospectifs-pour-l-aviation---analyse-nergtique-et-dcarbonation--F-H-_JR10443850</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -749,19 +748,19 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Title: data analyst | LOCATION UNVERIFIED: Germany</t>
+          <t>Title: carbon | LOCATION UNVERIFIED: Toulouse Area</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb Munich</t>
+          <t>Siemens Energy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -771,7 +770,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Manager, Environmental Health, Safety and Sustainability - Safety</t>
+          <t>Data Analyst im Bereich Manufacturing (m/w/d)</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -779,12 +778,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>San Diego - CA - US</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://bristolmyerssquibb.wd5.myworkdayjobs.com/BMS/job/San-Diego---CA---US/Manager--Environmental-Health--Safety-and-Sustainability---Safety_R1607841</t>
+          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Data-Analyst-im-Bereich-Manufacturing-m-w-d/305767</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -794,14 +793,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Title: sustainability | LOCATION UNVERIFIED: San Diego - CA - US</t>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Germany</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -816,11 +815,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Manager, Environmental Health, Safety and Sustainability – Environmental Compliance</t>
+          <t>Manager, Environmental Health, Safety and Sustainability - Safety</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -829,7 +828,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://bristolmyerssquibb.wd5.myworkdayjobs.com/BMS/job/San-Diego---CA---US/Manager--Environmental-Health--Safety-and-Sustainability---Environmental-Compliance_R1607843</t>
+          <t>https://bristolmyerssquibb.wd5.myworkdayjobs.com/BMS/job/San-Diego---CA---US/Manager--Environmental-Health--Safety-and-Sustainability---Safety_R1607841</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -846,12 +845,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Bristol Myers Squibb Munich</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -861,7 +860,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Human Rights and Sustainability Compliance</t>
+          <t>Manager, Environmental Health, Safety and Sustainability – Environmental Compliance</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -869,12 +868,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bucharest</t>
+          <t>San Diego - CA - US</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://accenture.wd103.myworkdayjobs.com/AccentureCareers/job/Bucharest/Human-Rights-and-Sustainability-Compliance_R00363151</t>
+          <t>https://bristolmyerssquibb.wd5.myworkdayjobs.com/BMS/job/San-Diego---CA---US/Manager--Environmental-Health--Safety-and-Sustainability---Environmental-Compliance_R1607843</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -884,7 +883,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Title: sustainability | LOCATION UNVERIFIED: Bucharest</t>
+          <t>Title: sustainability | LOCATION UNVERIFIED: San Diego - CA - US</t>
         </is>
       </c>
     </row>
@@ -896,7 +895,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Infineon Technologies</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -906,20 +905,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HR Data Analyst Trainee (f/m/div)</t>
+          <t>Human Rights and Sustainability Compliance</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Porto, Porto District,PT</t>
+          <t>Bucharest</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://jobs.infineon.com/careers/job/563808972279882</t>
+          <t>https://accenture.wd103.myworkdayjobs.com/AccentureCareers/job/Bucharest/Human-Rights-and-Sustainability-Compliance_R00363151</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -929,19 +928,19 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Title: data analyst | LOCATION UNVERIFIED: Porto, Porto District,PT</t>
+          <t>Title: sustainability | LOCATION UNVERIFIED: Bucharest</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Airbus</t>
+          <t>Infineon Technologies</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -951,20 +950,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Environmental Test Engineer</t>
+          <t>HR Data Analyst Trainee (f/m/div)</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Porto, Porto District,PT</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Stevenage/Environmental-Test-Engineer_JR10408723</t>
+          <t>https://jobs.infineon.com/careers/job/563808972279882</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -974,19 +973,19 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Title: environmental | LOCATION UNVERIFIED: Stevenage</t>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Porto, Porto District,PT</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Amgen Munich</t>
+          <t>Airbus</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -996,7 +995,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Environmental Health &amp; Safety Manager</t>
+          <t>Environmental Test Engineer</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1004,12 +1003,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>US - California - South San Francisco</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://amgen.wd1.myworkdayjobs.com/Careers/job/US---California---South-San-Francisco/Environmental-Health---Safety-Manager_R-258423-1</t>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Stevenage/Environmental-Test-Engineer_JR10408723</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1019,69 +1018,74 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Title: environmental | LOCATION UNVERIFIED: US - California - South San Francisco</t>
+          <t>Title: environmental | LOCATION UNVERIFIED: Stevenage</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Amgen Munich</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Environmental Health &amp; Safety Manager</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>US - California - South San Francisco</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://amgen.wd1.myworkdayjobs.com/Careers/job/US---California---South-San-Francisco/Environmental-Health---Safety-Manager_R-258423-1</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Title: environmental | LOCATION UNVERIFIED: US - California - South San Francisco</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>Environmental Management Specialist (f/m/d)</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>4</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Parsdorf, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/5009977101</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Title: environmental</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>FlixMobility</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Commercial Data Analyst Mexico City Regular</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1089,12 +1093,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mexico City</t>
+          <t>Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://flix.careers/job/?jobid=8364246002</t>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/5009977101</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1104,7 +1108,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Title: data analyst | LOCATION UNVERIFIED: Mexico City</t>
+          <t>Title: environmental</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1125,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Jr. Financial Planning &amp; Reporting Specialist (m/f/d) Sofia Regular</t>
+          <t>Commercial Data Analyst Mexico City Regular</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1129,12 +1133,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sofia</t>
+          <t>Mexico City</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://flix.careers/job/?jobid=8891299002</t>
+          <t>https://flix.careers/job/?jobid=8364246002</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1144,7 +1148,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Title: reporting specialist | LOCATION UNVERIFIED: Sofia</t>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Mexico City</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1178,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://flix.careers/job/?jobid=8622257002</t>
+          <t>https://flix.careers/job/?jobid=8891299002</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1189,14 +1193,9 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Stryker Munich</t>
+          <t>FlixMobility</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1206,7 +1205,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Service Associate - Detroit, MI - Sustainability Solutions</t>
+          <t>Jr. Financial Planning &amp; Reporting Specialist (m/f/d) Sofia Regular</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1214,12 +1213,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Detroit, Michigan</t>
+          <t>Sofia</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://stryker.wd1.myworkdayjobs.com/StrykerCareers/job/Detroit-Michigan/Service-Associate---Detroit--MI---Sustainability-Solutions_R576161</t>
+          <t>https://flix.careers/job/?jobid=8622257002</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1229,14 +1228,14 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Title: sustainability | LOCATION UNVERIFIED: Detroit, Michigan</t>
+          <t>Title: reporting specialist | LOCATION UNVERIFIED: Sofia</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1251,7 +1250,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Service Associate - Salt Lake City, Utah - Sustainability Solutions</t>
+          <t>Service Associate - Detroit, MI - Sustainability Solutions</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1259,12 +1258,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Salt Lake City, Utah</t>
+          <t>Detroit, Michigan</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://stryker.wd1.myworkdayjobs.com/StrykerCareers/job/Salt-Lake-City-Utah/Service-Associate---Salt-Lake-City--Utah---Sustainability-Solutions_R575799</t>
+          <t>https://stryker.wd1.myworkdayjobs.com/StrykerCareers/job/Detroit-Michigan/Service-Associate---Detroit--MI---Sustainability-Solutions_R576161</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1274,19 +1273,19 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Title: sustainability | LOCATION UNVERIFIED: Salt Lake City, Utah</t>
+          <t>Title: sustainability | LOCATION UNVERIFIED: Detroit, Michigan</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Airbus</t>
+          <t>Stryker Munich</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1296,7 +1295,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>A400M Fleet maintenance data analyst</t>
+          <t>Service Associate - Salt Lake City, Utah - Sustainability Solutions</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1304,12 +1303,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Getafe Area</t>
+          <t>Salt Lake City, Utah</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Getafe-Area/A400M-Fleet-maintenance-data-analyst_JR10448810-1</t>
+          <t>https://stryker.wd1.myworkdayjobs.com/StrykerCareers/job/Salt-Lake-City-Utah/Service-Associate---Salt-Lake-City--Utah---Sustainability-Solutions_R575799</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1319,19 +1318,19 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Title: data analyst | LOCATION UNVERIFIED: Getafe Area</t>
+          <t>Title: sustainability | LOCATION UNVERIFIED: Salt Lake City, Utah</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Salesforce Munich</t>
+          <t>Airbus</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1341,7 +1340,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Technical Data Analyst</t>
+          <t>A400M Fleet maintenance data analyst</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1349,12 +1348,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mexico - Mexico City</t>
+          <t>Getafe Area</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://salesforce.wd12.myworkdayjobs.com/External_Career_Site/job/Mexico---Mexico-City/System-Senior-Analyst_JR364924-1</t>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Getafe-Area/A400M-Fleet-maintenance-data-analyst_JR10448810-1</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1364,19 +1363,19 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Title: data analyst | LOCATION UNVERIFIED: Mexico - Mexico City</t>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Getafe Area</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Airbus</t>
+          <t>Salesforce Munich</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1386,20 +1385,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Stage 2027 - Stagiaire en Atténuation des effets non-CO2 de l'aviation (F/H)</t>
+          <t>Technical Data Analyst</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Toulouse Area</t>
+          <t>Mexico - Mexico City</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Toulouse-Area/Stage-2027---Stagiaire-en-Attnuation-des-effets-non-CO2-de-l-aviation--F-H-_JR10443593</t>
+          <t>https://salesforce.wd12.myworkdayjobs.com/External_Career_Site/job/Mexico---Mexico-City/System-Senior-Analyst_JR364924-1</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1409,14 +1408,14 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Title: co2 | LOCATION UNVERIFIED: Toulouse Area</t>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Mexico - Mexico City</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1431,7 +1430,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Combat Business Planning and Reporting Analyst (Temp Agency)</t>
+          <t>Stage 2027 - Stagiaire en Atténuation des effets non-CO2 de l'aviation (F/H)</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1439,12 +1438,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Getafe Area</t>
+          <t>Toulouse Area</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Getafe-Area/Combat-Business-Planning-and-Reporting-Analyst--Temp-Agency-_JR10450246</t>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Toulouse-Area/Stage-2027---Stagiaire-en-Attnuation-des-effets-non-CO2-de-l-aviation--F-H-_JR10443593</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1454,14 +1453,14 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Title: reporting analyst | LOCATION UNVERIFIED: Getafe Area</t>
+          <t>Title: co2 | LOCATION UNVERIFIED: Toulouse Area</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1476,7 +1475,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Stage 2027- Data Analyst &amp; AI - Corporate Audit (h/f)</t>
+          <t>Combat Business Planning and Reporting Analyst (Temp Agency)</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1484,79 +1483,79 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>Getafe Area</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Getafe-Area/Combat-Business-Planning-and-Reporting-Analyst--Temp-Agency-_JR10450246</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Title: reporting analyst | LOCATION UNVERIFIED: Getafe Area</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Stage 2027- Data Analyst &amp; AI - Corporate Audit (h/f)</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>Toulouse Area</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Toulouse-Area/Stage-2027--Data-Analyst---AI---Corporate-Audit--h-f-_JR10445497</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>Title: data analyst | LOCATION UNVERIFIED: Toulouse Area</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Stryker Munich</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Environmental, Health &amp; Safety Manager (Onsite)</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Tijuana, Mexico</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>https://stryker.wd1.myworkdayjobs.com/StrykerCareers/job/Tijuana-Mexico/Environmental--Health---Safety-Manager-_R564100</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>Title: environmental | LOCATION UNVERIFIED: Tijuana, Mexico</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Airbus</t>
+          <t>Stryker Munich</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1566,20 +1565,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>STAGE 2027 - Data Analyste en qualité logistique (h/f)</t>
+          <t>Environmental, Health &amp; Safety Manager (Onsite)</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tremblay-en-France</t>
+          <t>Tijuana, Mexico</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Tremblay-en-France/STAGE-2027---Data-Analyste-en-qualit-logistique--h-f-_JR10443345</t>
+          <t>https://stryker.wd1.myworkdayjobs.com/StrykerCareers/job/Tijuana-Mexico/Environmental--Health---Safety-Manager-_R564100</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1589,14 +1588,14 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Title: data analyst | LOCATION UNVERIFIED: Tremblay-en-France</t>
+          <t>Title: environmental | LOCATION UNVERIFIED: Tijuana, Mexico</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1611,7 +1610,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>STAGE 2027 - Finance Data Analyst (m/f)</t>
+          <t>STAGE 2027 - Data Analyste en qualité logistique (h/f)</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1619,12 +1618,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Marseille Area</t>
+          <t>Tremblay-en-France</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Marseille-Area/XMLNAME---Internship---Offer-Evaluation-digitalization---Finance-BI-Analyst--m-f--_JR10443902</t>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Tremblay-en-France/STAGE-2027---Data-Analyste-en-qualit-logistique--h-f-_JR10443345</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1634,19 +1633,19 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Title: data analyst | LOCATION UNVERIFIED: Marseille Area</t>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Tremblay-en-France</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sun Oct 25 02:00:00 UTC 2026</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>Airbus</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1656,15 +1655,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Systemingenieur für Radar Environmental Simulator (w/m/d)</t>
+          <t>STAGE 2027 - Finance Data Analyst (m/f)</t>
         </is>
       </c>
       <c r="E28" t="n">
         <v>2</v>
       </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Marseille Area</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/Ulm-Systemingenieur-f%C3%BCr-Radar-Environmental-Simulator-%28wmd%29-89077/1365917055/</t>
+          <t>https://ag.wd3.myworkdayjobs.com/Airbus/job/Marseille-Area/XMLNAME---Internship---Offer-Evaluation-digitalization---Finance-BI-Analyst--m-f--_JR10443902</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1674,19 +1678,19 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Title: environmental | LOCATION UNVERIFIED: none</t>
+          <t>Title: data analyst | LOCATION UNVERIFIED: Marseille Area</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>Sun Oct 25 02:00:00 UTC 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Workday Munich</t>
+          <t>Hensoldt</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1696,28 +1700,68 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Reporting Analyst, Workday Reporting</t>
+          <t>Systemingenieur für Radar Environmental Simulator (w/m/d)</t>
         </is>
       </c>
       <c r="E29" t="n">
         <v>2</v>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/Ulm-Systemingenieur-f%C3%BCr-Radar-Environmental-Simulator-%28wmd%29-89077/1365917055/</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Title: environmental | LOCATION UNVERIFIED: none</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Workday Munich</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Reporting Analyst, Workday Reporting</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>IND.Pune</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>https://workday.wd5.myworkdayjobs.com/Workday/job/INDPune/Reporting-Analyst--Workday-Reporting_JR-0110733</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Direct role</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Direct role</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
         <is>
           <t>Title: reporting analyst | LOCATION UNVERIFIED: IND.Pune</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -618,45 +618,45 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Sat Oct 31 02:01:00 UTC 2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>EY Germany</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>Forward Deployed Data and AI Business Analyst</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" t="n">
         <v>10</v>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Warszawa, PL, 00-124 +5 more…</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>https://careers.ey.com/ey/job/Warszawa-Forward-Deployed-Data-and-AI-Business-Analyst-00-124/1443899933/</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Related role</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Responsibilities: ghg_accounting, data_methodology, stakeholders | LOCATION UNVERIFIED: Warszawa, PL, 00-124 +5 more…</t>
         </is>
@@ -665,7 +665,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -800,7 +800,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -845,7 +845,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -890,7 +890,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1025,7 +1025,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1235,7 +1235,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1280,7 +1280,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1325,7 +1325,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1370,7 +1370,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1460,7 +1460,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1505,7 +1505,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1550,7 +1550,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1595,7 +1595,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1640,7 +1640,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1725,7 +1725,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
